--- a/docs/专业综合实习/01_评分表和标书/鱼你有图_技术评分表.xlsx
+++ b/docs/专业综合实习/01_评分表和标书/鱼你有图_技术评分表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29320" windowHeight="12860"/>
+    <workbookView windowWidth="20750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="打分表" sheetId="1" r:id="rId1"/>
@@ -160,11 +160,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.0"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="180" formatCode="0.0"/>
   </numFmts>
   <fonts count="34">
     <font>
@@ -815,19 +815,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1011,10 +1011,10 @@
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1032,10 +1032,10 @@
     <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1053,7 +1053,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1588,7 +1588,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultColWidth="9.88392857142857" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9.88181818181818" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="6" style="1" customWidth="1"/>
     <col min="2" max="2" width="18" style="1" customWidth="1"/>
@@ -1598,7 +1598,7 @@
     <col min="6" max="6" width="8" style="1" customWidth="1"/>
     <col min="7" max="9" width="12" style="1" customWidth="1"/>
     <col min="10" max="10" width="10" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.88392857142857" style="1"/>
+    <col min="11" max="16384" width="9.88181818181818" style="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10">
@@ -1667,7 +1667,9 @@
         <v>6</v>
       </c>
       <c r="G3" s="11"/>
-      <c r="H3" s="12"/>
+      <c r="H3" s="12">
+        <v>5</v>
+      </c>
       <c r="I3" s="12">
         <v>5</v>
       </c>
@@ -1696,13 +1698,15 @@
         <v>15</v>
       </c>
       <c r="G4" s="11"/>
-      <c r="H4" s="12"/>
+      <c r="H4" s="12">
+        <v>10</v>
+      </c>
       <c r="I4" s="12">
         <v>8</v>
       </c>
       <c r="J4" s="12">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" ht="96" customHeight="1" spans="1:10">
@@ -1725,7 +1729,9 @@
         <v>8</v>
       </c>
       <c r="G5" s="11"/>
-      <c r="H5" s="12"/>
+      <c r="H5" s="12">
+        <v>6</v>
+      </c>
       <c r="I5" s="12">
         <v>6</v>
       </c>
@@ -1754,13 +1760,15 @@
         <v>7</v>
       </c>
       <c r="G6" s="11"/>
-      <c r="H6" s="12"/>
+      <c r="H6" s="12">
+        <v>4</v>
+      </c>
       <c r="I6" s="12">
         <v>3</v>
       </c>
       <c r="J6" s="12">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="7" ht="82" customHeight="1" spans="1:10">
@@ -1783,13 +1791,15 @@
         <v>5</v>
       </c>
       <c r="G7" s="11"/>
-      <c r="H7" s="12"/>
+      <c r="H7" s="12">
+        <v>5</v>
+      </c>
       <c r="I7" s="12">
         <v>4</v>
       </c>
       <c r="J7" s="12">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="8" ht="82" customHeight="1" spans="1:10">
@@ -1812,13 +1822,15 @@
         <v>5</v>
       </c>
       <c r="G8" s="11"/>
-      <c r="H8" s="12"/>
+      <c r="H8" s="12">
+        <v>4</v>
+      </c>
       <c r="I8" s="12">
         <v>3</v>
       </c>
       <c r="J8" s="12">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="9" ht="95" customHeight="1" spans="1:10">
@@ -1841,7 +1853,9 @@
         <v>4</v>
       </c>
       <c r="G9" s="11"/>
-      <c r="H9" s="12"/>
+      <c r="H9" s="12">
+        <v>4</v>
+      </c>
       <c r="I9" s="12">
         <v>4</v>
       </c>
@@ -1868,7 +1882,7 @@
       </c>
       <c r="H10" s="19">
         <f>SUM(H3:H9)</f>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I10" s="19">
         <f>SUM(I3:I9)</f>
@@ -1876,7 +1890,7 @@
       </c>
       <c r="J10" s="19">
         <f>SUM(J3:J9)</f>
-        <v>33</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="11" ht="46" customHeight="1" spans="1:10">
@@ -1927,13 +1941,13 @@
       <formula1>0</formula1>
       <formula2>7</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="分值超出范围" error="本项打分应在0到5之间。" sqref="G7:I7 G8:I8" errorStyle="warning">
-      <formula1>0</formula1>
-      <formula2>5</formula2>
-    </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="分值超出范围" error="本项打分应在0到4之间。" sqref="G9:I9" errorStyle="warning">
       <formula1>0</formula1>
       <formula2>4</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="分值超出范围" error="本项打分应在0到5之间。" sqref="G7:I8" errorStyle="warning">
+      <formula1>0</formula1>
+      <formula2>5</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/专业综合实习/01_评分表和标书/鱼你有图_技术评分表.xlsx
+++ b/docs/专业综合实习/01_评分表和标书/鱼你有图_技术评分表.xlsx
@@ -1666,7 +1666,9 @@
       <c r="F3" s="10">
         <v>6</v>
       </c>
-      <c r="G3" s="11"/>
+      <c r="G3" s="11">
+        <v>4</v>
+      </c>
       <c r="H3" s="12">
         <v>5</v>
       </c>
@@ -1675,7 +1677,7 @@
       </c>
       <c r="J3" s="12">
         <f t="shared" ref="J3:J9" si="0">IF(COUNTA(G3:I3)=0,"",AVERAGE(G3:I3))</f>
-        <v>5</v>
+        <v>4.66666666666667</v>
       </c>
     </row>
     <row r="4" ht="91" customHeight="1" spans="1:10">
@@ -1697,7 +1699,9 @@
       <c r="F4" s="10">
         <v>15</v>
       </c>
-      <c r="G4" s="11"/>
+      <c r="G4" s="11">
+        <v>8</v>
+      </c>
       <c r="H4" s="12">
         <v>10</v>
       </c>
@@ -1706,7 +1710,7 @@
       </c>
       <c r="J4" s="12">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8.66666666666667</v>
       </c>
     </row>
     <row r="5" ht="96" customHeight="1" spans="1:10">
@@ -1728,7 +1732,9 @@
       <c r="F5" s="10">
         <v>8</v>
       </c>
-      <c r="G5" s="11"/>
+      <c r="G5" s="11">
+        <v>7</v>
+      </c>
       <c r="H5" s="12">
         <v>6</v>
       </c>
@@ -1737,7 +1743,7 @@
       </c>
       <c r="J5" s="12">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>6.33333333333333</v>
       </c>
     </row>
     <row r="6" ht="98" customHeight="1" spans="1:10">
@@ -1759,7 +1765,9 @@
       <c r="F6" s="10">
         <v>7</v>
       </c>
-      <c r="G6" s="11"/>
+      <c r="G6" s="11">
+        <v>5</v>
+      </c>
       <c r="H6" s="12">
         <v>4</v>
       </c>
@@ -1768,7 +1776,7 @@
       </c>
       <c r="J6" s="12">
         <f t="shared" si="0"/>
-        <v>3.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" ht="82" customHeight="1" spans="1:10">
@@ -1790,7 +1798,9 @@
       <c r="F7" s="10">
         <v>5</v>
       </c>
-      <c r="G7" s="11"/>
+      <c r="G7" s="11">
+        <v>4</v>
+      </c>
       <c r="H7" s="12">
         <v>5</v>
       </c>
@@ -1799,7 +1809,7 @@
       </c>
       <c r="J7" s="12">
         <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>4.33333333333333</v>
       </c>
     </row>
     <row r="8" ht="82" customHeight="1" spans="1:10">
@@ -1821,7 +1831,9 @@
       <c r="F8" s="10">
         <v>5</v>
       </c>
-      <c r="G8" s="11"/>
+      <c r="G8" s="11">
+        <v>4</v>
+      </c>
       <c r="H8" s="12">
         <v>4</v>
       </c>
@@ -1830,7 +1842,7 @@
       </c>
       <c r="J8" s="12">
         <f t="shared" si="0"/>
-        <v>3.5</v>
+        <v>3.66666666666667</v>
       </c>
     </row>
     <row r="9" ht="95" customHeight="1" spans="1:10">
@@ -1852,7 +1864,9 @@
       <c r="F9" s="10">
         <v>4</v>
       </c>
-      <c r="G9" s="11"/>
+      <c r="G9" s="11">
+        <v>4</v>
+      </c>
       <c r="H9" s="12">
         <v>4</v>
       </c>
@@ -1878,7 +1892,7 @@
       </c>
       <c r="G10" s="18">
         <f>SUM(G3:G9)</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H10" s="19">
         <f>SUM(H3:H9)</f>
@@ -1890,7 +1904,7 @@
       </c>
       <c r="J10" s="19">
         <f>SUM(J3:J9)</f>
-        <v>35.5</v>
+        <v>35.6666666666667</v>
       </c>
     </row>
     <row r="11" ht="46" customHeight="1" spans="1:10">
